--- a/public/exports/29189757.xlsx
+++ b/public/exports/29189757.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257717</t>
+          <t xml:space="preserve">311257874</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">

--- a/public/exports/29189757.xlsx
+++ b/public/exports/29189757.xlsx
@@ -9739,7 +9739,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255967</t>
+          <t xml:space="preserve">311255968</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255967</t>
+          <t xml:space="preserve">311255968</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">

--- a/public/exports/29189757.xlsx
+++ b/public/exports/29189757.xlsx
@@ -9739,7 +9739,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255968</t>
+          <t xml:space="preserve">311255967</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
